--- a/web/files/九龙-九龙塘-Park College.xlsx
+++ b/web/files/九龙-九龙塘-Park College.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -830,7 +830,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1595,7 +1595,7 @@
           <t>A | 3040呎 (4+房)
 $12800万
 $42,105/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -1603,7 +1603,7 @@
           <t>B | 3022呎 (4+房)
 $15000万
 $49,636/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
           <t>A | 1478呎 (3房)
 $6000万
 $40,595/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -1627,7 +1627,7 @@
           <t>B | 1463呎 (3房)
 $6000万
 $41,012/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -1643,7 +1643,7 @@
           <t>A | 1478呎 (3房)
 $5900万
 $39,919/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
           <t>B | 1463呎 (3房)
 $5900万
 $40,328/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
           <t>A | 1478呎 (3房)
 $6000万
 $40,595/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -1691,7 +1691,7 @@
           <t>A | 1405呎 (3房)
 $6300万
 $44,840/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -1699,7 +1699,7 @@
           <t>B | 1390呎 (3房)
 $6000万
 $43,165/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr"/>

--- a/web/files/九龙-九龙塘-Park College.xlsx
+++ b/web/files/九龙-九龙塘-Park College.xlsx
@@ -1423,23 +1423,19 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>148800000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>48627</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1448,12 +1444,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1463,7 +1459,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1534,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -1712,12 +1708,12 @@
       </c>
       <c r="B10" s="21" t="inlineStr"/>
       <c r="C10" s="21" t="inlineStr"/>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>GV | 3060呎 (4+房)
-招标单位
--
-(在售)</t>
+$14880万
+$48,627/呎
+(26年-08月-19日)</t>
         </is>
       </c>
     </row>
